--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,8 +1207,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
     <col width="15" customWidth="1" style="3" min="4" max="4"/>
@@ -1352,70 +1352,183 @@
       </c>
     </row>
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>XG2024053114233416141967857</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>XG2024111210523019950586917</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>16141967857</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>31828566</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>19950586917</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>31831672</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2024-05-31 14:23:34</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>2024-11-12 10:52:30</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2024111210523019507047772</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19507047772</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31831672</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2024-11-12 10:52:30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customFormat="1" customHeight="1" s="2"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XG2024111210523019950766711</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19950766711</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31831672</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2024-11-12 10:52:30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:W1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="I2" showErrorMessage="1" showInputMessage="1" allowBlank="1" prompt="如果是第三方平台收款，请设置第三方平台收款的金额，并且在豌豆收款金额中填写应该与豌豆结算金额，如果不是请设置为0"/>
-    <dataValidation sqref="K3:K4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="K3" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>[1]支付方式!#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024111210523019950586917</t>
+          <t>XG2024120913442513672435927</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>19950586917</t>
+          <t>13672435927</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31831672</t>
+          <t>20532903</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-11-12 10:52:30</t>
+          <t>2024-12-09 13:44:25</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,120 +1403,6 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2024111210523019507047772</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19507047772</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31831672</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2024-11-12 10:52:30</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>XG2024111210523019950766711</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>19950766711</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>31831672</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2024-11-12 10:52:30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024120913442513672435927</t>
+          <t>XG2024121614452415239625802</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>13672435927</t>
+          <t>15239625802</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>20532903</t>
+          <t>31825515</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-09 13:44:25</t>
+          <t>2024-12-16 14:45:24</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121614452415239625802</t>
+          <t>XG2024121810453819384911406</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>15239625802</t>
+          <t>19384911406</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-16 14:45:24</t>
+          <t>2024-12-18 10:45:38</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121810453819384911406</t>
+          <t>XG2024121820524718707699952</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>19384911406</t>
+          <t>18707699952</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31825515</t>
+          <t>20528464</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-18 10:45:38</t>
+          <t>2024-12-18 20:52:47</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,6 +1403,63 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2024121820524718707699953</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>18707699953</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20528464</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2024-12-18 20:52:47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024121820524718707699952</t>
+          <t>XG2024122511283813177271407</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>18707699952</t>
+          <t>13177271407</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>20528464</t>
+          <t>31825515</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-18 20:52:47</t>
+          <t>2024-12-25 11:28:38</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,63 +1403,6 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2024121820524718707699953</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>18707699953</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>20528464</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2024-12-18 20:52:47</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024122511283813177271407</t>
+          <t>XG2024122616075114656948998</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>13177271407</t>
+          <t>14656948998</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31825515</t>
+          <t>20532903</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-25 11:28:38</t>
+          <t>2024-12-26 16:07:51</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,6 +1403,63 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2024122616075114660206373</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>14660206373</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20532903</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9.99</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2024-12-26 16:07:51</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2024122616075114656948998</t>
+          <t>XG2025011410433012823586543</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>14656948998</t>
+          <t>12823586543</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>20532903</t>
+          <t>31832305</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2024-12-26 16:07:51</t>
+          <t>2025-01-14 10:43:30</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XG2024122616075114660206373</t>
+          <t>XG2025011410433017282610008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14660206373</t>
+          <t>17282610008</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20532903</t>
+          <t>31832305</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2024-12-26 16:07:51</t>
+          <t>2025-01-14 10:43:30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1460,6 +1460,120 @@
         </is>
       </c>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XG2025011410433012827373736</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12827373736</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31832305</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12.67</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-01-14 10:43:30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XG2025011410433017282825345</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17282825345</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31832305</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12.67</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-01-14 10:43:30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>481608</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025011410433012823586543</t>
+          <t>XG2025021010133717198967557</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>12823586543</t>
+          <t>17198967557</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31832305</t>
+          <t>31825515</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-01-14 10:43:30</t>
+          <t>2025-02-10 10:13:37</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,177 +1403,6 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2025011410433017282610008</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>17282610008</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31832305</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12.67</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-01-14 10:43:30</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>XG2025011410433012827373736</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12827373736</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>31832305</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12.67</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-01-14 10:43:30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>XG2025011410433017282825345</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17282825345</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>31832305</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12.67</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2025-01-14 10:43:30</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>481608</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025021010133717198967557</t>
+          <t>XG2025042517320515257039547</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>17198967557</t>
+          <t>15257039547</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31825515</t>
+          <t>31832305</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-02-10 10:13:37</t>
+          <t>2025-04-24 17:32:05</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025042517320515257039547</t>
+          <t>XG2025050816450313025050602</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>15257039547</t>
+          <t>13025050602</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31832305</t>
+          <t>31830439</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-04-24 17:32:05</t>
+          <t>2025-05-08 16:45:03</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L3" s="0" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" s="0" t="inlineStr">
@@ -1403,6 +1403,63 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2025050816450318707699952</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>18707699952</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31830439</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-05-08 16:45:03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025050816450313025050602</t>
+          <t>XG2025061711453418820102219</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>13025050602</t>
+          <t>18820102219</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31830439</t>
+          <t>31828570</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-05-08 16:45:03</t>
+          <t>2025-06-17 11:45:34</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,63 +1403,6 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2025050816450318707699952</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>18707699952</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31830439</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-05-08 16:45:03</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025061711453418820102219</t>
+          <t>XG202508071355171232323230</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>18820102219</t>
+          <t>1232323230</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31828570</t>
+          <t>31835572</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-06-17 11:45:34</t>
+          <t>2025-08-07 13:55:17</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG202508071355171232323230</t>
+          <t>XG2025081714044613724011223</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>1232323230</t>
+          <t>13724011223</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31835572</t>
+          <t>31828570</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-08-07 13:55:17</t>
+          <t>2025-08-17 14:04:46</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025081714044613724011223</t>
+          <t>XG2025081914533118900001003</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>13724011223</t>
+          <t>18900001003</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31828570</t>
+          <t>31832305</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-08-17 14:04:46</t>
+          <t>2025-08-19 14:53:31</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22400" windowHeight="10080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -936,8 +936,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="导入主表"/>
       <sheetName val="获得原因"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025081914533118900001003</t>
+          <t>XG2025090111531211914392908</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>18900001003</t>
+          <t>11914392908</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-08-19 14:53:31</t>
+          <t>2025-09-01 11:53:12</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1413,8 +1413,8 @@
     <mergeCell ref="A1:W1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="I2" showErrorMessage="1" showInputMessage="1" allowBlank="1" prompt="如果是第三方平台收款，请设置第三方平台收款的金额，并且在豌豆收款金额中填写应该与豌豆结算金额，如果不是请设置为0"/>
-    <dataValidation sqref="K3" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="I2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="如果是第三方平台收款，请设置第三方平台收款的金额，并且在豌豆收款金额中填写应该与豌豆结算金额，如果不是请设置为0"/>
+    <dataValidation sqref="K3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>[1]支付方式!#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025090111531211914392908</t>
+          <t>XG2025091115243717665794542</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>11914392908</t>
+          <t>17665794542</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-09-01 11:53:12</t>
+          <t>2025-09-11 15:24:37</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025091115243717665794542</t>
+          <t>XG2025101014174314601533298</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>17665794542</t>
+          <t>14601533298</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31832305</t>
+          <t>31835572</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-09-11 15:24:37</t>
+          <t>2025-10-10 14:17:43</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1403,6 +1403,120 @@
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XG2025101014174313460153322</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13460153322</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31835572</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-10-10 14:17:43</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XG2025101014174313460153333</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13460153333</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31835572</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-10-10 14:17:43</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="34.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025101014174314601533298</t>
+          <t>XG2025102218451015819903128</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1362,6 +1362,7 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C3" s="0" t="inlineStr"/>
       <c r="D3" s="0" t="inlineStr">
         <is>
           <t>86</t>
@@ -1369,22 +1370,24 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>14601533298</t>
-        </is>
-      </c>
+          <t>15819903128</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31835572</t>
+          <t>31832911</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-10-10 14:17:43</t>
+          <t>2025-10-22 18:45:10</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -1402,121 +1405,8 @@
           <t>1999</t>
         </is>
       </c>
+      <c r="N3" s="0" t="inlineStr"/>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XG2025101014174313460153322</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>13460153322</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31835572</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-10-10 14:17:43</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>XG2025101014174313460153333</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>13460153333</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>31835572</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-10-10 14:17:43</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025102218451015819903128</t>
+          <t>XG2025102418101017010001193</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1370,24 +1370,24 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>15819903128</t>
+          <t>17010001193</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31832911</t>
+          <t>31827746</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-10-22 18:45:10</t>
+          <t>2025-10-24 18:10:10</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">

--- a/API/CreateData/biaoda.xlsx
+++ b/API/CreateData/biaoda.xlsx
@@ -1354,7 +1354,7 @@
     <row r="3" ht="60" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>XG2025102418101017010001193</t>
+          <t>XG2026042115514513295982032</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1370,24 +1370,24 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>17010001193</t>
+          <t>13295982032</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>31827746</t>
+          <t>31832911</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>2025-10-24 18:10:10</t>
+          <t>2026-04-21 15:51:45</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
